--- a/all_metrics_chow_choco.xlsx
+++ b/all_metrics_chow_choco.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gowustl-my.sharepoint.com/personal/murrell_wustl_edu/Documents/Documents/Github/PredictingObesity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E61B417-79E3-48DE-ADF8-15D3340D99BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{4E61B417-79E3-48DE-ADF8-15D3340D99BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FB775CE-E0EA-4C73-9ED4-A9F4826F56B6}"/>
   <bookViews>
-    <workbookView xWindow="1965" yWindow="540" windowWidth="23505" windowHeight="14445" xr2:uid="{05588D14-5A53-4C63-9503-85D2CF250AC3}"/>
+    <workbookView xWindow="2505" yWindow="870" windowWidth="23505" windowHeight="14445" xr2:uid="{05588D14-5A53-4C63-9503-85D2CF250AC3}"/>
   </bookViews>
   <sheets>
     <sheet name="All metrics" sheetId="1" r:id="rId1"/>
@@ -490,7 +490,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -541,12 +541,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -566,29 +560,29 @@
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -926,6 +920,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B722B20E-7088-4963-9D4C-0BC746EF0704}">
   <dimension ref="A1:CV41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1248,11 +1247,13 @@
       <c r="F2" s="10">
         <v>1.28</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="14">
+        <v>3.93</v>
+      </c>
+      <c r="H2" s="14">
         <v>0.43</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>0.34399999999999997</v>
       </c>
       <c r="J2" s="10">
@@ -1548,11 +1549,13 @@
       <c r="F3" s="10">
         <v>0.84</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="14">
+        <v>5.55</v>
+      </c>
+      <c r="H3" s="14">
         <v>0.38</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="12">
+      <c r="I3" s="11">
         <v>0.30130000000000001</v>
       </c>
       <c r="J3" s="10">
@@ -1780,11 +1783,13 @@
       <c r="F4" s="10">
         <v>1.22</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="14">
+        <v>4.41</v>
+      </c>
+      <c r="H4" s="14">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="12">
+      <c r="I4" s="11">
         <v>0.45450000000000002</v>
       </c>
       <c r="J4" s="10">
@@ -2080,11 +2085,13 @@
       <c r="F5" s="10">
         <v>0.91</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="14">
+        <v>4.87</v>
+      </c>
+      <c r="H5" s="14">
         <v>0.36</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <v>0.31259999999999999</v>
       </c>
       <c r="J5" s="10">
@@ -2380,11 +2387,13 @@
       <c r="F6" s="10">
         <v>0.56000000000000005</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="14">
+        <v>4.13</v>
+      </c>
+      <c r="H6" s="14">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
         <v>0.28339999999999999</v>
       </c>
       <c r="J6" s="10">
@@ -2680,11 +2689,13 @@
       <c r="F7" s="10">
         <v>1.43</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="14">
+        <v>4.51</v>
+      </c>
+      <c r="H7" s="14">
         <v>0.28000000000000003</v>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <v>0.55789999999999995</v>
       </c>
       <c r="J7" s="10">
@@ -2980,11 +2991,13 @@
       <c r="F8" s="10">
         <v>0.68</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="14">
+        <v>3.27</v>
+      </c>
+      <c r="H8" s="14">
         <v>0.44</v>
       </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="12">
+      <c r="I8" s="11">
         <v>0.5081</v>
       </c>
       <c r="J8" s="10">
@@ -3280,11 +3293,13 @@
       <c r="F9" s="10">
         <v>1.4</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="14">
+        <v>5.51</v>
+      </c>
+      <c r="H9" s="14">
         <v>0.31</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="12">
+      <c r="I9" s="11">
         <v>0.31019999999999998</v>
       </c>
       <c r="J9" s="10">
@@ -3578,11 +3593,13 @@
       <c r="F10" s="10">
         <v>1.7</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="14">
+        <v>4.34</v>
+      </c>
+      <c r="H10" s="14">
         <v>0.15</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="12">
+      <c r="I10" s="11">
         <v>0.43780000000000002</v>
       </c>
       <c r="J10" s="10">
@@ -3878,11 +3895,13 @@
       <c r="F11" s="10">
         <v>0.91</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="14">
+        <v>4.07</v>
+      </c>
+      <c r="H11" s="14">
         <v>0.13</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="12">
+      <c r="I11" s="11">
         <v>0.31169999999999998</v>
       </c>
       <c r="J11" s="10">
@@ -4178,11 +4197,13 @@
       <c r="F12" s="10">
         <v>0.98</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="14">
+        <v>5.43</v>
+      </c>
+      <c r="H12" s="14">
         <v>0.91</v>
       </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="12">
+      <c r="I12" s="11">
         <v>0.30590000000000001</v>
       </c>
       <c r="J12" s="10">
@@ -4478,11 +4499,13 @@
       <c r="F13" s="10">
         <v>1.1100000000000001</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="14">
+        <v>4.79</v>
+      </c>
+      <c r="H13" s="14">
         <v>0.23</v>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="12">
+      <c r="I13" s="11">
         <v>0.2059</v>
       </c>
       <c r="J13" s="10">
@@ -4778,11 +4801,13 @@
       <c r="F14" s="10">
         <v>0.99</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="14">
+        <v>5.27</v>
+      </c>
+      <c r="H14" s="14">
         <v>0.63</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="12">
+      <c r="I14" s="11">
         <v>0.2382</v>
       </c>
       <c r="J14" s="10">
@@ -5034,11 +5059,13 @@
       <c r="F15" s="10">
         <v>0.99</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="14">
+        <v>5.85</v>
+      </c>
+      <c r="H15" s="14">
         <v>0.56999999999999995</v>
       </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="12">
+      <c r="I15" s="11">
         <v>0.47099999999999997</v>
       </c>
       <c r="J15" s="10">
@@ -5334,11 +5361,13 @@
       <c r="F16" s="10">
         <v>1.19</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="14">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H16" s="14">
         <v>0.49</v>
       </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="12">
+      <c r="I16" s="11">
         <v>0.29870000000000002</v>
       </c>
       <c r="J16" s="10">
@@ -5634,11 +5663,13 @@
       <c r="F17" s="10">
         <v>0.95</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="14">
+        <v>5.73</v>
+      </c>
+      <c r="H17" s="14">
         <v>0.67</v>
       </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="12">
+      <c r="I17" s="11">
         <v>0.38850000000000001</v>
       </c>
       <c r="J17" s="10">
@@ -5934,11 +5965,13 @@
       <c r="F18" s="10">
         <v>0.62</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="14">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="H18" s="14">
         <v>0.63</v>
       </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="12">
+      <c r="I18" s="11">
         <v>0.1978</v>
       </c>
       <c r="J18" s="10">
@@ -6234,11 +6267,13 @@
       <c r="F19" s="10">
         <v>1.29</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="14">
+        <v>5.38</v>
+      </c>
+      <c r="H19" s="14">
         <v>0.36</v>
       </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="12">
+      <c r="I19" s="11">
         <v>0.44869999999999999</v>
       </c>
       <c r="J19" s="10">
@@ -6534,11 +6569,13 @@
       <c r="F20" s="10">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="14">
+        <v>4.84</v>
+      </c>
+      <c r="H20" s="14">
         <v>0.25</v>
       </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="12">
+      <c r="I20" s="11">
         <v>0.37880000000000003</v>
       </c>
       <c r="J20" s="10">
@@ -6834,11 +6871,13 @@
       <c r="F21" s="10">
         <v>0.69</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="14">
+        <v>5.29</v>
+      </c>
+      <c r="H21" s="14">
         <v>0.71</v>
       </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="12">
+      <c r="I21" s="11">
         <v>0.50509999999999999</v>
       </c>
       <c r="J21" s="10">
@@ -10446,7 +10485,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="F35" s="2"/>
-      <c r="G35" s="14">
+      <c r="G35" s="12">
         <v>5.21</v>
       </c>
       <c r="H35" s="10">

--- a/all_metrics_chow_choco.xlsx
+++ b/all_metrics_chow_choco.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gowustl-my.sharepoint.com/personal/murrell_wustl_edu/Documents/Documents/Github/PredictingObesity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{4E61B417-79E3-48DE-ADF8-15D3340D99BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FB775CE-E0EA-4C73-9ED4-A9F4826F56B6}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{4E61B417-79E3-48DE-ADF8-15D3340D99BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{269F1D7F-D84B-4653-84FB-8A0C2BA5D037}"/>
   <bookViews>
-    <workbookView xWindow="2505" yWindow="870" windowWidth="23505" windowHeight="14445" xr2:uid="{05588D14-5A53-4C63-9503-85D2CF250AC3}"/>
+    <workbookView xWindow="2160" yWindow="525" windowWidth="23505" windowHeight="14445" xr2:uid="{05588D14-5A53-4C63-9503-85D2CF250AC3}"/>
   </bookViews>
   <sheets>
     <sheet name="All metrics" sheetId="1" r:id="rId1"/>
@@ -50,9 +50,6 @@
     <t>Starting Weight</t>
   </si>
   <si>
-    <t>Weight Change 24hr HFD</t>
-  </si>
-  <si>
     <t>Daily Chow Consumption</t>
   </si>
   <si>
@@ -462,6 +459,9 @@
   </si>
   <si>
     <t>ChowHFD_191</t>
+  </si>
+  <si>
+    <t>24hr HFD Weight Gain</t>
   </si>
 </sst>
 </file>
@@ -579,10 +579,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -599,6 +599,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -940,292 +944,292 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="AA1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AD1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AF1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AM1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AR1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AS1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AT1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AU1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="7" t="s">
+      <c r="AV1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="7" t="s">
+      <c r="AW1" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="7" t="s">
+      <c r="AX1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="7" t="s">
+      <c r="AY1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="7" t="s">
+      <c r="AZ1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="7" t="s">
+      <c r="BA1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="7" t="s">
+      <c r="BB1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="7" t="s">
+      <c r="BC1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="7" t="s">
+      <c r="BD1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="7" t="s">
+      <c r="BE1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="7" t="s">
+      <c r="BF1" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="7" t="s">
+      <c r="BG1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="7" t="s">
+      <c r="BH1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="7" t="s">
+      <c r="BI1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="7" t="s">
+      <c r="BJ1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="7" t="s">
+      <c r="BK1" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="7" t="s">
+      <c r="BL1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="7" t="s">
+      <c r="BM1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="7" t="s">
+      <c r="BN1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="7" t="s">
+      <c r="BO1" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="7" t="s">
+      <c r="BP1" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="7" t="s">
+      <c r="BQ1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="7" t="s">
+      <c r="BR1" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="7" t="s">
+      <c r="BS1" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="7" t="s">
+      <c r="BT1" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="7" t="s">
+      <c r="BU1" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="7" t="s">
+      <c r="BV1" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" s="7" t="s">
+      <c r="BW1" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" s="7" t="s">
+      <c r="BX1" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" s="7" t="s">
+      <c r="BY1" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="BY1" s="7" t="s">
+      <c r="BZ1" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="BZ1" s="7" t="s">
+      <c r="CA1" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="CA1" s="7" t="s">
+      <c r="CB1" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="CB1" s="7" t="s">
+      <c r="CC1" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" s="8" t="s">
+      <c r="CD1" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="8" t="s">
+      <c r="CE1" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" s="8" t="s">
+      <c r="CF1" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="CF1" s="8" t="s">
+      <c r="CG1" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="CG1" s="8" t="s">
+      <c r="CH1" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="CH1" s="8" t="s">
+      <c r="CI1" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="CI1" s="8" t="s">
+      <c r="CJ1" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="CJ1" s="8" t="s">
+      <c r="CK1" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="CK1" s="8" t="s">
+      <c r="CL1" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="CL1" s="8" t="s">
+      <c r="CM1" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="CM1" s="8" t="s">
+      <c r="CN1" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="CN1" s="8" t="s">
+      <c r="CO1" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="CO1" s="8" t="s">
+      <c r="CP1" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="CP1" s="9" t="s">
+      <c r="CQ1" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="CQ1" s="9" t="s">
+      <c r="CR1" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="CR1" s="9" t="s">
+      <c r="CS1" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="CS1" s="9" t="s">
+      <c r="CT1" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="CT1" s="9" t="s">
+      <c r="CU1" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="CU1" s="9" t="s">
+      <c r="CV1" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="CV1" s="9" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:100" x14ac:dyDescent="0.25">
@@ -1233,10 +1237,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="D2" s="10">
         <v>26.62</v>
@@ -1247,10 +1251,10 @@
       <c r="F2" s="10">
         <v>1.28</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="13">
         <v>3.93</v>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="13">
         <v>0.43</v>
       </c>
       <c r="I2" s="11">
@@ -1535,10 +1539,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D3" s="10">
         <v>26.23</v>
@@ -1549,10 +1553,10 @@
       <c r="F3" s="10">
         <v>0.84</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="13">
         <v>5.55</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="13">
         <v>0.38</v>
       </c>
       <c r="I3" s="11">
@@ -1769,10 +1773,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D4" s="10">
         <v>27.03</v>
@@ -1783,10 +1787,10 @@
       <c r="F4" s="10">
         <v>1.22</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="13">
         <v>4.41</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>0.14000000000000001</v>
       </c>
       <c r="I4" s="11">
@@ -2071,10 +2075,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D5" s="10">
         <v>26.64</v>
@@ -2085,10 +2089,10 @@
       <c r="F5" s="10">
         <v>0.91</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="13">
         <v>4.87</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>0.36</v>
       </c>
       <c r="I5" s="11">
@@ -2373,10 +2377,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D6" s="10">
         <v>23.75</v>
@@ -2387,10 +2391,10 @@
       <c r="F6" s="10">
         <v>0.56000000000000005</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="13">
         <v>4.13</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <v>0.14000000000000001</v>
       </c>
       <c r="I6" s="11">
@@ -2675,10 +2679,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D7" s="10">
         <v>27.54</v>
@@ -2689,10 +2693,10 @@
       <c r="F7" s="10">
         <v>1.43</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="13">
         <v>4.51</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="13">
         <v>0.28000000000000003</v>
       </c>
       <c r="I7" s="11">
@@ -2977,10 +2981,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D8" s="10">
         <v>26.44</v>
@@ -2991,10 +2995,10 @@
       <c r="F8" s="10">
         <v>0.68</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="13">
         <v>3.27</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <v>0.44</v>
       </c>
       <c r="I8" s="11">
@@ -3279,10 +3283,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D9" s="10">
         <v>28.54</v>
@@ -3293,10 +3297,10 @@
       <c r="F9" s="10">
         <v>1.4</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="13">
         <v>5.51</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="13">
         <v>0.31</v>
       </c>
       <c r="I9" s="11">
@@ -3579,10 +3583,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D10" s="10">
         <v>27.39</v>
@@ -3593,10 +3597,10 @@
       <c r="F10" s="10">
         <v>1.7</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="13">
         <v>4.34</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="13">
         <v>0.15</v>
       </c>
       <c r="I10" s="11">
@@ -3881,10 +3885,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D11" s="10">
         <v>25.37</v>
@@ -3895,10 +3899,10 @@
       <c r="F11" s="10">
         <v>0.91</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="13">
         <v>4.07</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="13">
         <v>0.13</v>
       </c>
       <c r="I11" s="11">
@@ -4183,10 +4187,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D12" s="10">
         <v>28.99</v>
@@ -4197,10 +4201,10 @@
       <c r="F12" s="10">
         <v>0.98</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="13">
         <v>5.43</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="13">
         <v>0.91</v>
       </c>
       <c r="I12" s="11">
@@ -4485,10 +4489,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D13" s="10">
         <v>27.35</v>
@@ -4499,10 +4503,10 @@
       <c r="F13" s="10">
         <v>1.1100000000000001</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="13">
         <v>4.79</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="13">
         <v>0.23</v>
       </c>
       <c r="I13" s="11">
@@ -4787,10 +4791,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D14" s="10">
         <v>26.36</v>
@@ -4801,10 +4805,10 @@
       <c r="F14" s="10">
         <v>0.99</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="13">
         <v>5.27</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="13">
         <v>0.63</v>
       </c>
       <c r="I14" s="11">
@@ -5045,10 +5049,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D15" s="10">
         <v>24.77</v>
@@ -5059,10 +5063,10 @@
       <c r="F15" s="10">
         <v>0.99</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="13">
         <v>5.85</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="13">
         <v>0.56999999999999995</v>
       </c>
       <c r="I15" s="11">
@@ -5347,10 +5351,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D16" s="10">
         <v>26.66</v>
@@ -5361,10 +5365,10 @@
       <c r="F16" s="10">
         <v>1.19</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="13">
         <v>5.0999999999999996</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="13">
         <v>0.49</v>
       </c>
       <c r="I16" s="11">
@@ -5649,10 +5653,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D17" s="10">
         <v>29.03</v>
@@ -5663,10 +5667,10 @@
       <c r="F17" s="10">
         <v>0.95</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="13">
         <v>5.73</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="13">
         <v>0.67</v>
       </c>
       <c r="I17" s="11">
@@ -5951,10 +5955,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D18" s="10">
         <v>25.17</v>
@@ -5965,10 +5969,10 @@
       <c r="F18" s="10">
         <v>0.62</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="13">
         <v>5.0599999999999996</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="13">
         <v>0.63</v>
       </c>
       <c r="I18" s="11">
@@ -6253,10 +6257,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D19" s="10">
         <v>26.57</v>
@@ -6267,10 +6271,10 @@
       <c r="F19" s="10">
         <v>1.29</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="13">
         <v>5.38</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="13">
         <v>0.36</v>
       </c>
       <c r="I19" s="11">
@@ -6555,10 +6559,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D20" s="10">
         <v>27.75</v>
@@ -6569,10 +6573,10 @@
       <c r="F20" s="10">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="13">
         <v>4.84</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="13">
         <v>0.25</v>
       </c>
       <c r="I20" s="11">
@@ -6857,10 +6861,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D21" s="10">
         <v>26.02</v>
@@ -6871,10 +6875,10 @@
       <c r="F21" s="10">
         <v>0.69</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="13">
         <v>5.29</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="13">
         <v>0.71</v>
       </c>
       <c r="I21" s="11">
@@ -7159,10 +7163,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="D22" s="10">
         <v>25.2</v>
@@ -7445,10 +7449,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D23" s="10">
         <v>25.6</v>
@@ -7731,10 +7735,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D24" s="10">
         <v>21.3</v>
@@ -8017,10 +8021,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D25" s="10">
         <v>26.4</v>
@@ -8273,10 +8277,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D26" s="10">
         <v>26.4</v>
@@ -8514,10 +8518,10 @@
       <c r="CI26" s="10">
         <v>9</v>
       </c>
-      <c r="CJ26" s="13">
+      <c r="CJ26" s="14">
         <v>101.06125040000001</v>
       </c>
-      <c r="CK26" s="13"/>
+      <c r="CK26" s="14"/>
       <c r="CL26" s="2"/>
       <c r="CM26" s="2"/>
       <c r="CN26" s="2"/>
@@ -8549,10 +8553,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D27" s="10">
         <v>23.9</v>
@@ -8835,10 +8839,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D28" s="10">
         <v>24.1</v>
@@ -9091,10 +9095,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D29" s="10">
         <v>25.3</v>
@@ -9279,10 +9283,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D30" s="10">
         <v>23.8</v>
@@ -9422,10 +9426,10 @@
       <c r="CI30" s="10">
         <v>7</v>
       </c>
-      <c r="CJ30" s="13">
+      <c r="CJ30" s="14">
         <v>128.01321329999999</v>
       </c>
-      <c r="CK30" s="13"/>
+      <c r="CK30" s="14"/>
       <c r="CL30" s="2"/>
       <c r="CM30" s="2"/>
       <c r="CN30" s="2"/>
@@ -9457,10 +9461,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D31" s="10">
         <v>24.1</v>
@@ -9615,10 +9619,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D32" s="10">
         <v>23.1</v>
@@ -9901,10 +9905,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D33" s="10">
         <v>23.1</v>
@@ -10187,10 +10191,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D34" s="10">
         <v>25.5</v>
@@ -10473,10 +10477,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D35" s="10">
         <v>24.9</v>
@@ -10714,10 +10718,10 @@
       <c r="CI35" s="10">
         <v>3</v>
       </c>
-      <c r="CJ35" s="13">
+      <c r="CJ35" s="14">
         <v>122.1753564</v>
       </c>
-      <c r="CK35" s="13"/>
+      <c r="CK35" s="14"/>
       <c r="CL35" s="2"/>
       <c r="CM35" s="2"/>
       <c r="CN35" s="2"/>
@@ -10749,10 +10753,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D36" s="10">
         <v>23.6</v>
@@ -11035,10 +11039,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D37" s="10">
         <v>25</v>
@@ -11321,10 +11325,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D38" s="10">
         <v>22.9</v>
@@ -11562,10 +11566,10 @@
       <c r="CI38" s="10">
         <v>5</v>
       </c>
-      <c r="CJ38" s="13">
+      <c r="CJ38" s="14">
         <v>114.6221786</v>
       </c>
-      <c r="CK38" s="13"/>
+      <c r="CK38" s="14"/>
       <c r="CL38" s="2"/>
       <c r="CM38" s="2"/>
       <c r="CN38" s="2"/>
@@ -11597,10 +11601,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D39" s="10">
         <v>22.7</v>
@@ -11883,10 +11887,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D40" s="10">
         <v>23.3</v>
@@ -12169,10 +12173,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D41" s="10">
         <v>23.6</v>
